--- a/VerveStacks_DEU_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_DEU_grids_kan10/SysSettings.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DEU_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7876B1-D189-4375-9E63-808D988F2507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118C1048-148D-4F68-A57C-0F5CDF0CF776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="12683" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
-    <sheet name="grids" sheetId="7" r:id="rId2"/>
-    <sheet name="fuels" sheetId="2" r:id="rId3"/>
-    <sheet name="TimePeriods" sheetId="3" r:id="rId4"/>
+    <sheet name="fuels" sheetId="2" r:id="rId2"/>
+    <sheet name="TimePeriods" sheetId="3" r:id="rId3"/>
+    <sheet name="grids" sheetId="7" r:id="rId4"/>
     <sheet name="System Settings" sheetId="4" r:id="rId5"/>
     <sheet name="Constants" sheetId="5" r:id="rId6"/>
     <sheet name="reporting options" sheetId="6" r:id="rId7"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="384">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -245,9 +245,6 @@
     <t>IMP*Z</t>
   </si>
   <si>
-    <t>IMPDEMZ</t>
-  </si>
-  <si>
     <t>~Currencies</t>
   </si>
   <si>
@@ -698,12 +695,66 @@
     <t>ELC_BatIn</t>
   </si>
   <si>
+    <t>set</t>
+  </si>
+  <si>
+    <t>ctype</t>
+  </si>
+  <si>
+    <t>ELC4H</t>
+  </si>
+  <si>
+    <t>First 5 hours of surplus electricity from VRE generation</t>
+  </si>
+  <si>
+    <t>DAYNITE</t>
+  </si>
+  <si>
+    <t>ELC8H</t>
+  </si>
+  <si>
+    <t>6-10 hours of surplus electricity from VRE generation</t>
+  </si>
+  <si>
+    <t>DEF_E</t>
+  </si>
+  <si>
+    <t>Electricity that was missing at the hourly level</t>
+  </si>
+  <si>
+    <t>DEF_C</t>
+  </si>
+  <si>
+    <t>VRE Capacity deficit to be covered by dispatchable techs</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>HET</t>
+  </si>
+  <si>
+    <t>low temperature heat</t>
+  </si>
+  <si>
+    <t>season</t>
+  </si>
+  <si>
+    <t>LTHEAT</t>
+  </si>
+  <si>
+    <t>IMPDEMZ,IMPDUCZ</t>
+  </si>
+  <si>
+    <t>IMPDUCZ</t>
+  </si>
+  <si>
+    <t>invcost</t>
+  </si>
+  <si>
     <t>DEU</t>
   </si>
   <si>
-    <t>set</t>
-  </si>
-  <si>
     <t>region</t>
   </si>
   <si>
@@ -1043,19 +1094,37 @@
     <t>~fi_comm</t>
   </si>
   <si>
-    <t>e_w1094015892-380_DEU</t>
-  </si>
-  <si>
-    <t>grid node -- way/1094015892-380</t>
+    <t>e_DE173-220_DEU</t>
+  </si>
+  <si>
+    <t>grid node -- DE173-220</t>
   </si>
   <si>
     <t>lo</t>
   </si>
   <si>
-    <t>e_w1128250704-380_DEU</t>
-  </si>
-  <si>
-    <t>grid node -- way/1128250704-380</t>
+    <t>e_DE206-220_DEU</t>
+  </si>
+  <si>
+    <t>grid node -- DE206-220</t>
+  </si>
+  <si>
+    <t>e_w108797675-380_DEU</t>
+  </si>
+  <si>
+    <t>grid node -- way/108797675-380</t>
+  </si>
+  <si>
+    <t>e_w1128250707-380_DEU</t>
+  </si>
+  <si>
+    <t>grid node -- way/1128250707-380</t>
+  </si>
+  <si>
+    <t>e_w143882655-380_DEU</t>
+  </si>
+  <si>
+    <t>grid node -- way/143882655-380</t>
   </si>
   <si>
     <t>e_w157328339-380_DEU</t>
@@ -1070,40 +1139,28 @@
     <t>grid node -- way/170123812-400</t>
   </si>
   <si>
-    <t>e_w24757392-380_DEU</t>
-  </si>
-  <si>
-    <t>grid node -- way/24757392-380</t>
-  </si>
-  <si>
-    <t>e_w24839976-380_DEU</t>
-  </si>
-  <si>
-    <t>grid node -- way/24839976-380</t>
-  </si>
-  <si>
     <t>e_w26472665-380_DEU</t>
   </si>
   <si>
     <t>grid node -- way/26472665-380</t>
   </si>
   <si>
-    <t>e_w29309786-380_DEU</t>
-  </si>
-  <si>
-    <t>grid node -- way/29309786-380</t>
-  </si>
-  <si>
-    <t>e_w42410916-380_DEU</t>
-  </si>
-  <si>
-    <t>grid node -- way/42410916-380</t>
-  </si>
-  <si>
-    <t>e_w42488850-380_DEU</t>
-  </si>
-  <si>
-    <t>grid node -- way/42488850-380</t>
+    <t>e_w275466323_DEU</t>
+  </si>
+  <si>
+    <t>grid node -- way/275466323</t>
+  </si>
+  <si>
+    <t>e_w29084374-380_DEU</t>
+  </si>
+  <si>
+    <t>grid node -- way/29084374-380</t>
+  </si>
+  <si>
+    <t>e_w449010725-380_DEU</t>
+  </si>
+  <si>
+    <t>grid node -- way/449010725-380</t>
   </si>
   <si>
     <t>e_w525964617_DEU</t>
@@ -1112,16 +1169,22 @@
     <t>grid node -- way/525964617</t>
   </si>
   <si>
-    <t>e_w76246159-380_DEU</t>
-  </si>
-  <si>
-    <t>grid node -- way/76246159-380</t>
-  </si>
-  <si>
-    <t>e_w88916034-380_DEU</t>
-  </si>
-  <si>
-    <t>grid node -- way/88916034-380</t>
+    <t>e_w68532663-220_DEU</t>
+  </si>
+  <si>
+    <t>grid node -- way/68532663-220</t>
+  </si>
+  <si>
+    <t>e_w870598507_DEU</t>
+  </si>
+  <si>
+    <t>grid node -- way/870598507</t>
+  </si>
+  <si>
+    <t>e_w940919943_DEU</t>
+  </si>
+  <si>
+    <t>grid node -- way/940919943</t>
   </si>
   <si>
     <t>e_w952346322-380_DEU</t>
@@ -3518,7 +3581,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="F4" t="s">
         <v>36</v>
@@ -3542,411 +3605,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{186C8E61-067C-4613-879B-EEFE2FA3C2E3}">
-  <dimension ref="B3:I18"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <sheetData>
-    <row r="3" spans="2:9">
-      <c r="B3" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9">
-      <c r="B4" t="s">
-        <v>220</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" t="s">
-        <v>221</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9">
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>334</v>
-      </c>
-      <c r="D5" t="s">
-        <v>219</v>
-      </c>
-      <c r="E5" t="s">
-        <v>335</v>
-      </c>
-      <c r="F5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" t="s">
-        <v>336</v>
-      </c>
-      <c r="I5" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9">
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>337</v>
-      </c>
-      <c r="D6" t="s">
-        <v>219</v>
-      </c>
-      <c r="E6" t="s">
-        <v>338</v>
-      </c>
-      <c r="F6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" t="s">
-        <v>336</v>
-      </c>
-      <c r="I6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9">
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>339</v>
-      </c>
-      <c r="D7" t="s">
-        <v>219</v>
-      </c>
-      <c r="E7" t="s">
-        <v>340</v>
-      </c>
-      <c r="F7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" t="s">
-        <v>336</v>
-      </c>
-      <c r="I7" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9">
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>341</v>
-      </c>
-      <c r="D8" t="s">
-        <v>219</v>
-      </c>
-      <c r="E8" t="s">
-        <v>342</v>
-      </c>
-      <c r="F8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" t="s">
-        <v>336</v>
-      </c>
-      <c r="I8" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9">
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
-        <v>343</v>
-      </c>
-      <c r="D9" t="s">
-        <v>219</v>
-      </c>
-      <c r="E9" t="s">
-        <v>344</v>
-      </c>
-      <c r="F9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" t="s">
-        <v>336</v>
-      </c>
-      <c r="I9" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9">
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" t="s">
-        <v>345</v>
-      </c>
-      <c r="D10" t="s">
-        <v>219</v>
-      </c>
-      <c r="E10" t="s">
-        <v>346</v>
-      </c>
-      <c r="F10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" t="s">
-        <v>336</v>
-      </c>
-      <c r="I10" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9">
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" t="s">
-        <v>347</v>
-      </c>
-      <c r="D11" t="s">
-        <v>219</v>
-      </c>
-      <c r="E11" t="s">
-        <v>348</v>
-      </c>
-      <c r="F11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" t="s">
-        <v>336</v>
-      </c>
-      <c r="I11" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9">
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" t="s">
-        <v>349</v>
-      </c>
-      <c r="D12" t="s">
-        <v>219</v>
-      </c>
-      <c r="E12" t="s">
-        <v>350</v>
-      </c>
-      <c r="F12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" t="s">
-        <v>336</v>
-      </c>
-      <c r="I12" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9">
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" t="s">
-        <v>351</v>
-      </c>
-      <c r="D13" t="s">
-        <v>219</v>
-      </c>
-      <c r="E13" t="s">
-        <v>352</v>
-      </c>
-      <c r="F13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G13" t="s">
-        <v>35</v>
-      </c>
-      <c r="H13" t="s">
-        <v>336</v>
-      </c>
-      <c r="I13" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9">
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" t="s">
-        <v>353</v>
-      </c>
-      <c r="D14" t="s">
-        <v>219</v>
-      </c>
-      <c r="E14" t="s">
-        <v>354</v>
-      </c>
-      <c r="F14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" t="s">
-        <v>35</v>
-      </c>
-      <c r="H14" t="s">
-        <v>336</v>
-      </c>
-      <c r="I14" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9">
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" t="s">
-        <v>355</v>
-      </c>
-      <c r="D15" t="s">
-        <v>219</v>
-      </c>
-      <c r="E15" t="s">
-        <v>356</v>
-      </c>
-      <c r="F15" t="s">
-        <v>25</v>
-      </c>
-      <c r="G15" t="s">
-        <v>35</v>
-      </c>
-      <c r="H15" t="s">
-        <v>336</v>
-      </c>
-      <c r="I15" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9">
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" t="s">
-        <v>357</v>
-      </c>
-      <c r="D16" t="s">
-        <v>219</v>
-      </c>
-      <c r="E16" t="s">
-        <v>358</v>
-      </c>
-      <c r="F16" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16" t="s">
-        <v>35</v>
-      </c>
-      <c r="H16" t="s">
-        <v>336</v>
-      </c>
-      <c r="I16" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>359</v>
-      </c>
-      <c r="D17" t="s">
-        <v>219</v>
-      </c>
-      <c r="E17" t="s">
-        <v>360</v>
-      </c>
-      <c r="F17" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" t="s">
-        <v>35</v>
-      </c>
-      <c r="H17" t="s">
-        <v>336</v>
-      </c>
-      <c r="I17" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9">
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" t="s">
-        <v>361</v>
-      </c>
-      <c r="D18" t="s">
-        <v>219</v>
-      </c>
-      <c r="E18" t="s">
-        <v>362</v>
-      </c>
-      <c r="F18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H18" t="s">
-        <v>336</v>
-      </c>
-      <c r="I18" t="s">
-        <v>224</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2F298A9-BCD9-4ABF-BE3B-9D1BDD3E7001}">
   <dimension ref="B3:S59"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -4006,13 +3664,13 @@
         <v>16</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>10</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="P4" s="5" t="s">
         <v>11</v>
@@ -4041,13 +3699,13 @@
         <v>17</v>
       </c>
       <c r="N5" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="O5" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P5" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="Q5" t="s">
         <v>25</v>
@@ -4056,7 +3714,7 @@
         <v>35</v>
       </c>
       <c r="S5" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" spans="2:19">
@@ -4064,7 +3722,7 @@
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E6" t="s">
         <v>18</v>
@@ -4073,13 +3731,13 @@
         <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="O6" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P6" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="Q6" t="s">
         <v>25</v>
@@ -4088,7 +3746,7 @@
         <v>35</v>
       </c>
       <c r="S6" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" spans="2:19">
@@ -4096,7 +3754,7 @@
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -4105,13 +3763,13 @@
         <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="O7" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P7" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="Q7" t="s">
         <v>25</v>
@@ -4120,7 +3778,7 @@
         <v>35</v>
       </c>
       <c r="S7" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="2:19">
@@ -4137,13 +3795,13 @@
         <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="O8" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P8" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="Q8" t="s">
         <v>25</v>
@@ -4152,7 +3810,7 @@
         <v>35</v>
       </c>
       <c r="S8" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="2:19">
@@ -4169,13 +3827,13 @@
         <v>17</v>
       </c>
       <c r="N9" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="O9" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P9" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="Q9" t="s">
         <v>25</v>
@@ -4184,7 +3842,7 @@
         <v>35</v>
       </c>
       <c r="S9" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="2:19">
@@ -4201,13 +3859,13 @@
         <v>17</v>
       </c>
       <c r="N10" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="O10" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P10" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="Q10" t="s">
         <v>25</v>
@@ -4216,7 +3874,7 @@
         <v>35</v>
       </c>
       <c r="S10" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" spans="2:19">
@@ -4233,13 +3891,13 @@
         <v>17</v>
       </c>
       <c r="N11" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="O11" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P11" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="Q11" t="s">
         <v>25</v>
@@ -4248,7 +3906,7 @@
         <v>35</v>
       </c>
       <c r="S11" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12" spans="2:19">
@@ -4256,7 +3914,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E12" t="s">
         <v>18</v>
@@ -4265,13 +3923,13 @@
         <v>17</v>
       </c>
       <c r="N12" t="s">
+        <v>254</v>
+      </c>
+      <c r="O12" t="s">
         <v>237</v>
       </c>
-      <c r="O12" t="s">
-        <v>219</v>
-      </c>
       <c r="P12" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="Q12" t="s">
         <v>25</v>
@@ -4280,7 +3938,7 @@
         <v>35</v>
       </c>
       <c r="S12" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" spans="2:19">
@@ -4297,13 +3955,13 @@
         <v>17</v>
       </c>
       <c r="N13" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="O13" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P13" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="Q13" t="s">
         <v>25</v>
@@ -4312,7 +3970,7 @@
         <v>35</v>
       </c>
       <c r="S13" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" spans="2:19">
@@ -4320,10 +3978,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
@@ -4332,13 +3990,13 @@
         <v>17</v>
       </c>
       <c r="N14" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="O14" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P14" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="Q14" t="s">
         <v>25</v>
@@ -4347,7 +4005,7 @@
         <v>35</v>
       </c>
       <c r="S14" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15" spans="2:19">
@@ -4355,10 +4013,10 @@
         <v>17</v>
       </c>
       <c r="C15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E15" t="s">
         <v>18</v>
@@ -4367,13 +4025,13 @@
         <v>17</v>
       </c>
       <c r="N15" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="O15" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P15" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="Q15" t="s">
         <v>25</v>
@@ -4382,7 +4040,7 @@
         <v>35</v>
       </c>
       <c r="S15" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" spans="2:19">
@@ -4411,13 +4069,13 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="O16" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P16" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="Q16" t="s">
         <v>25</v>
@@ -4426,33 +4084,39 @@
         <v>35</v>
       </c>
       <c r="S16" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="17" spans="2:19">
       <c r="B17" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="D17" t="s">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="E17" t="s">
         <v>18</v>
       </c>
+      <c r="F17" t="s">
+        <v>232</v>
+      </c>
+      <c r="G17" t="s">
+        <v>233</v>
+      </c>
       <c r="M17" t="s">
         <v>17</v>
       </c>
       <c r="N17" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="O17" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P17" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="Q17" t="s">
         <v>25</v>
@@ -4461,7 +4125,7 @@
         <v>35</v>
       </c>
       <c r="S17" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="18" spans="2:19">
@@ -4469,10 +4133,10 @@
         <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>202</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>203</v>
       </c>
       <c r="E18" t="s">
         <v>18</v>
@@ -4481,13 +4145,13 @@
         <v>17</v>
       </c>
       <c r="N18" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="O18" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P18" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
       <c r="Q18" t="s">
         <v>25</v>
@@ -4496,7 +4160,7 @@
         <v>35</v>
       </c>
       <c r="S18" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" spans="2:19">
@@ -4504,10 +4168,10 @@
         <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19" t="s">
         <v>18</v>
@@ -4516,13 +4180,13 @@
         <v>17</v>
       </c>
       <c r="N19" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="O19" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P19" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="Q19" t="s">
         <v>25</v>
@@ -4531,7 +4195,7 @@
         <v>35</v>
       </c>
       <c r="S19" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" spans="2:19">
@@ -4539,10 +4203,10 @@
         <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E20" t="s">
         <v>18</v>
@@ -4551,13 +4215,13 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="O20" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P20" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="Q20" t="s">
         <v>25</v>
@@ -4566,39 +4230,33 @@
         <v>35</v>
       </c>
       <c r="S20" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" spans="2:19">
       <c r="B21" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>197</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>198</v>
+        <v>33</v>
       </c>
       <c r="E21" t="s">
         <v>18</v>
       </c>
-      <c r="F21" t="s">
-        <v>35</v>
-      </c>
-      <c r="G21" t="s">
-        <v>25</v>
-      </c>
       <c r="M21" t="s">
         <v>17</v>
       </c>
       <c r="N21" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="O21" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P21" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="Q21" t="s">
         <v>25</v>
@@ -4607,33 +4265,39 @@
         <v>35</v>
       </c>
       <c r="S21" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="22" spans="2:19">
       <c r="B22" t="s">
-        <v>193</v>
+        <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D22" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E22" t="s">
-        <v>196</v>
+        <v>18</v>
+      </c>
+      <c r="F22" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" t="s">
+        <v>25</v>
       </c>
       <c r="M22" t="s">
         <v>17</v>
       </c>
       <c r="N22" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="O22" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P22" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="Q22" t="s">
         <v>25</v>
@@ -4642,30 +4306,33 @@
         <v>35</v>
       </c>
       <c r="S22" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="23" spans="2:19">
       <c r="B23" t="s">
+        <v>192</v>
+      </c>
+      <c r="C23" t="s">
         <v>193</v>
       </c>
-      <c r="C23" t="s">
-        <v>200</v>
+      <c r="D23" t="s">
+        <v>194</v>
       </c>
       <c r="E23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M23" t="s">
         <v>17</v>
       </c>
       <c r="N23" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="O23" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P23" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="Q23" t="s">
         <v>25</v>
@@ -4674,30 +4341,30 @@
         <v>35</v>
       </c>
       <c r="S23" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24" spans="2:19">
       <c r="B24" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M24" t="s">
         <v>17</v>
       </c>
       <c r="N24" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="O24" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P24" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="Q24" t="s">
         <v>25</v>
@@ -4706,21 +4373,30 @@
         <v>35</v>
       </c>
       <c r="S24" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="25" spans="2:19">
+      <c r="B25" t="s">
+        <v>192</v>
+      </c>
+      <c r="C25" t="s">
+        <v>200</v>
+      </c>
+      <c r="E25" t="s">
+        <v>195</v>
+      </c>
       <c r="M25" t="s">
         <v>17</v>
       </c>
       <c r="N25" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="O25" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P25" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="Q25" t="s">
         <v>25</v>
@@ -4729,7 +4405,7 @@
         <v>35</v>
       </c>
       <c r="S25" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="26" spans="2:19">
@@ -4737,13 +4413,13 @@
         <v>17</v>
       </c>
       <c r="N26" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="O26" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P26" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="Q26" t="s">
         <v>25</v>
@@ -4752,7 +4428,7 @@
         <v>35</v>
       </c>
       <c r="S26" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27" spans="2:19">
@@ -4760,13 +4436,13 @@
         <v>17</v>
       </c>
       <c r="N27" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="O27" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P27" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="Q27" t="s">
         <v>25</v>
@@ -4775,12 +4451,12 @@
         <v>35</v>
       </c>
       <c r="S27" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="28" spans="2:19" ht="17.649999999999999" thickBot="1">
       <c r="B28" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -4788,13 +4464,13 @@
         <v>17</v>
       </c>
       <c r="N28" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="O28" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P28" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="Q28" t="s">
         <v>25</v>
@@ -4803,30 +4479,30 @@
         <v>35</v>
       </c>
       <c r="S28" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29" spans="2:19" ht="15" thickTop="1" thickBot="1">
       <c r="B29" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C29" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>214</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>215</v>
       </c>
       <c r="M29" t="s">
         <v>17</v>
       </c>
       <c r="N29" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="O29" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P29" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="Q29" t="s">
         <v>25</v>
@@ -4835,30 +4511,30 @@
         <v>35</v>
       </c>
       <c r="S29" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="30" spans="2:19">
       <c r="B30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C30" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M30" t="s">
         <v>17</v>
       </c>
       <c r="N30" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="O30" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P30" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="Q30" t="s">
         <v>25</v>
@@ -4867,7 +4543,7 @@
         <v>35</v>
       </c>
       <c r="S30" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31" spans="2:19">
@@ -4875,13 +4551,13 @@
         <v>17</v>
       </c>
       <c r="N31" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="O31" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P31" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="Q31" t="s">
         <v>25</v>
@@ -4890,7 +4566,7 @@
         <v>35</v>
       </c>
       <c r="S31" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="32" spans="2:19">
@@ -4898,13 +4574,13 @@
         <v>17</v>
       </c>
       <c r="N32" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="O32" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P32" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="Q32" t="s">
         <v>25</v>
@@ -4913,21 +4589,21 @@
         <v>35</v>
       </c>
       <c r="S32" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="33" spans="13:19">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19">
       <c r="M33" t="s">
         <v>17</v>
       </c>
       <c r="N33" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="O33" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P33" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="Q33" t="s">
         <v>25</v>
@@ -4936,21 +4612,21 @@
         <v>35</v>
       </c>
       <c r="S33" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="34" spans="13:19">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19">
       <c r="M34" t="s">
         <v>17</v>
       </c>
       <c r="N34" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="O34" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P34" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="Q34" t="s">
         <v>25</v>
@@ -4959,21 +4635,21 @@
         <v>35</v>
       </c>
       <c r="S34" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="35" spans="13:19">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19">
       <c r="M35" t="s">
         <v>17</v>
       </c>
       <c r="N35" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="O35" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P35" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="Q35" t="s">
         <v>25</v>
@@ -4982,21 +4658,21 @@
         <v>35</v>
       </c>
       <c r="S35" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="36" spans="13:19">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="36" spans="2:19">
       <c r="M36" t="s">
         <v>17</v>
       </c>
       <c r="N36" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="O36" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P36" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="Q36" t="s">
         <v>25</v>
@@ -5005,21 +4681,21 @@
         <v>35</v>
       </c>
       <c r="S36" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="37" spans="13:19">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19">
       <c r="M37" t="s">
         <v>17</v>
       </c>
       <c r="N37" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="O37" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P37" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="Q37" t="s">
         <v>25</v>
@@ -5028,21 +4704,26 @@
         <v>35</v>
       </c>
       <c r="S37" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="38" spans="13:19">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="38" spans="2:19" ht="17.649999999999999" thickBot="1">
+      <c r="B38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
       <c r="M38" t="s">
         <v>17</v>
       </c>
       <c r="N38" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="O38" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P38" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="Q38" t="s">
         <v>25</v>
@@ -5051,21 +4732,39 @@
         <v>35</v>
       </c>
       <c r="S38" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="39" spans="13:19">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" ht="15" thickTop="1" thickBot="1">
+      <c r="B39" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>219</v>
+      </c>
       <c r="M39" t="s">
         <v>17</v>
       </c>
       <c r="N39" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="O39" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P39" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="Q39" t="s">
         <v>25</v>
@@ -5074,21 +4773,39 @@
         <v>35</v>
       </c>
       <c r="S39" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="40" spans="13:19">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="40" spans="2:19">
+      <c r="B40" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" t="s">
+        <v>220</v>
+      </c>
+      <c r="D40" t="s">
+        <v>221</v>
+      </c>
+      <c r="E40" t="s">
+        <v>84</v>
+      </c>
+      <c r="F40" t="s">
+        <v>222</v>
+      </c>
+      <c r="G40" t="s">
+        <v>25</v>
+      </c>
       <c r="M40" t="s">
         <v>17</v>
       </c>
       <c r="N40" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="O40" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P40" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="Q40" t="s">
         <v>25</v>
@@ -5097,21 +4814,36 @@
         <v>35</v>
       </c>
       <c r="S40" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="41" spans="2:19">
+      <c r="C41" t="s">
+        <v>223</v>
+      </c>
+      <c r="D41" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="41" spans="13:19">
+      <c r="E41" t="s">
+        <v>84</v>
+      </c>
+      <c r="F41" t="s">
+        <v>222</v>
+      </c>
+      <c r="G41" t="s">
+        <v>25</v>
+      </c>
       <c r="M41" t="s">
         <v>17</v>
       </c>
       <c r="N41" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="O41" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P41" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="Q41" t="s">
         <v>25</v>
@@ -5120,21 +4852,36 @@
         <v>35</v>
       </c>
       <c r="S41" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="42" spans="13:19">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19">
+      <c r="B42" t="s">
+        <v>192</v>
+      </c>
+      <c r="C42" t="s">
+        <v>225</v>
+      </c>
+      <c r="D42" t="s">
+        <v>226</v>
+      </c>
+      <c r="E42" t="s">
+        <v>84</v>
+      </c>
+      <c r="F42" t="s">
+        <v>222</v>
+      </c>
       <c r="M42" t="s">
         <v>17</v>
       </c>
       <c r="N42" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="O42" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P42" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="Q42" t="s">
         <v>25</v>
@@ -5143,21 +4890,33 @@
         <v>35</v>
       </c>
       <c r="S42" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="43" spans="13:19">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19">
+      <c r="C43" t="s">
+        <v>227</v>
+      </c>
+      <c r="D43" t="s">
+        <v>228</v>
+      </c>
+      <c r="E43" t="s">
+        <v>229</v>
+      </c>
+      <c r="F43" t="s">
+        <v>185</v>
+      </c>
       <c r="M43" t="s">
         <v>17</v>
       </c>
       <c r="N43" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="O43" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P43" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="Q43" t="s">
         <v>25</v>
@@ -5166,21 +4925,21 @@
         <v>35</v>
       </c>
       <c r="S43" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="44" spans="13:19">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19">
       <c r="M44" t="s">
         <v>17</v>
       </c>
       <c r="N44" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="O44" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P44" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="Q44" t="s">
         <v>25</v>
@@ -5189,21 +4948,21 @@
         <v>35</v>
       </c>
       <c r="S44" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="45" spans="13:19">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19">
       <c r="M45" t="s">
         <v>17</v>
       </c>
       <c r="N45" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="O45" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P45" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="Q45" t="s">
         <v>25</v>
@@ -5212,21 +4971,21 @@
         <v>35</v>
       </c>
       <c r="S45" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="46" spans="13:19">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19">
       <c r="M46" t="s">
         <v>17</v>
       </c>
       <c r="N46" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="O46" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P46" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="Q46" t="s">
         <v>25</v>
@@ -5235,21 +4994,21 @@
         <v>35</v>
       </c>
       <c r="S46" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="47" spans="13:19">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19">
       <c r="M47" t="s">
         <v>17</v>
       </c>
       <c r="N47" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="O47" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P47" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="Q47" t="s">
         <v>25</v>
@@ -5258,21 +5017,21 @@
         <v>35</v>
       </c>
       <c r="S47" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="48" spans="13:19">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19">
       <c r="M48" t="s">
         <v>17</v>
       </c>
       <c r="N48" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="O48" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P48" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="Q48" t="s">
         <v>25</v>
@@ -5281,7 +5040,7 @@
         <v>35</v>
       </c>
       <c r="S48" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="49" spans="13:19">
@@ -5289,13 +5048,13 @@
         <v>17</v>
       </c>
       <c r="N49" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="O49" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P49" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="Q49" t="s">
         <v>25</v>
@@ -5304,7 +5063,7 @@
         <v>35</v>
       </c>
       <c r="S49" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="50" spans="13:19">
@@ -5312,13 +5071,13 @@
         <v>17</v>
       </c>
       <c r="N50" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="O50" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P50" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="Q50" t="s">
         <v>25</v>
@@ -5327,7 +5086,7 @@
         <v>35</v>
       </c>
       <c r="S50" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="51" spans="13:19">
@@ -5335,13 +5094,13 @@
         <v>17</v>
       </c>
       <c r="N51" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="O51" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P51" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="Q51" t="s">
         <v>25</v>
@@ -5350,7 +5109,7 @@
         <v>35</v>
       </c>
       <c r="S51" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="52" spans="13:19">
@@ -5358,13 +5117,13 @@
         <v>17</v>
       </c>
       <c r="N52" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="O52" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P52" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="Q52" t="s">
         <v>25</v>
@@ -5373,7 +5132,7 @@
         <v>35</v>
       </c>
       <c r="S52" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="53" spans="13:19">
@@ -5381,13 +5140,13 @@
         <v>17</v>
       </c>
       <c r="N53" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="O53" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P53" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="Q53" t="s">
         <v>25</v>
@@ -5396,7 +5155,7 @@
         <v>35</v>
       </c>
       <c r="S53" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="54" spans="13:19">
@@ -5404,13 +5163,13 @@
         <v>17</v>
       </c>
       <c r="N54" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="O54" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P54" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="Q54" t="s">
         <v>25</v>
@@ -5419,7 +5178,7 @@
         <v>35</v>
       </c>
       <c r="S54" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="55" spans="13:19">
@@ -5427,13 +5186,13 @@
         <v>17</v>
       </c>
       <c r="N55" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="O55" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P55" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="Q55" t="s">
         <v>25</v>
@@ -5442,7 +5201,7 @@
         <v>35</v>
       </c>
       <c r="S55" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="56" spans="13:19">
@@ -5450,13 +5209,13 @@
         <v>17</v>
       </c>
       <c r="N56" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="O56" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P56" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="Q56" t="s">
         <v>25</v>
@@ -5465,7 +5224,7 @@
         <v>35</v>
       </c>
       <c r="S56" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="57" spans="13:19">
@@ -5473,13 +5232,13 @@
         <v>17</v>
       </c>
       <c r="N57" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="O57" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P57" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="Q57" t="s">
         <v>25</v>
@@ -5488,7 +5247,7 @@
         <v>35</v>
       </c>
       <c r="S57" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="58" spans="13:19">
@@ -5496,13 +5255,13 @@
         <v>17</v>
       </c>
       <c r="N58" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="O58" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P58" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="Q58" t="s">
         <v>25</v>
@@ -5511,7 +5270,7 @@
         <v>35</v>
       </c>
       <c r="S58" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="59" spans="13:19">
@@ -5519,13 +5278,13 @@
         <v>17</v>
       </c>
       <c r="N59" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="O59" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="P59" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="Q59" t="s">
         <v>25</v>
@@ -5534,7 +5293,7 @@
         <v>35</v>
       </c>
       <c r="S59" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -5545,7 +5304,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A39735C-B147-4873-BE33-BF7570891F36}">
   <dimension ref="B3:G33"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="12.75"/>
@@ -5820,6 +5579,463 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80CEBCE0-DDA8-4F5C-ADB5-47CDDDB304B1}">
+  <dimension ref="B3:I20"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetData>
+    <row r="3" spans="2:9">
+      <c r="B3" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
+      <c r="B4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9">
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>351</v>
+      </c>
+      <c r="D5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E5" t="s">
+        <v>352</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>353</v>
+      </c>
+      <c r="I5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9">
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D6" t="s">
+        <v>237</v>
+      </c>
+      <c r="E6" t="s">
+        <v>355</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" t="s">
+        <v>353</v>
+      </c>
+      <c r="I6" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9">
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>356</v>
+      </c>
+      <c r="D7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E7" t="s">
+        <v>357</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" t="s">
+        <v>353</v>
+      </c>
+      <c r="I7" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9">
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>358</v>
+      </c>
+      <c r="D8" t="s">
+        <v>237</v>
+      </c>
+      <c r="E8" t="s">
+        <v>359</v>
+      </c>
+      <c r="F8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" t="s">
+        <v>353</v>
+      </c>
+      <c r="I8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>360</v>
+      </c>
+      <c r="D9" t="s">
+        <v>237</v>
+      </c>
+      <c r="E9" t="s">
+        <v>361</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" t="s">
+        <v>353</v>
+      </c>
+      <c r="I9" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9">
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>362</v>
+      </c>
+      <c r="D10" t="s">
+        <v>237</v>
+      </c>
+      <c r="E10" t="s">
+        <v>363</v>
+      </c>
+      <c r="F10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" t="s">
+        <v>353</v>
+      </c>
+      <c r="I10" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9">
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>364</v>
+      </c>
+      <c r="D11" t="s">
+        <v>237</v>
+      </c>
+      <c r="E11" t="s">
+        <v>365</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" t="s">
+        <v>353</v>
+      </c>
+      <c r="I11" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9">
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>366</v>
+      </c>
+      <c r="D12" t="s">
+        <v>237</v>
+      </c>
+      <c r="E12" t="s">
+        <v>367</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" t="s">
+        <v>353</v>
+      </c>
+      <c r="I12" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9">
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>368</v>
+      </c>
+      <c r="D13" t="s">
+        <v>237</v>
+      </c>
+      <c r="E13" t="s">
+        <v>369</v>
+      </c>
+      <c r="F13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" t="s">
+        <v>353</v>
+      </c>
+      <c r="I13" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9">
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>370</v>
+      </c>
+      <c r="D14" t="s">
+        <v>237</v>
+      </c>
+      <c r="E14" t="s">
+        <v>371</v>
+      </c>
+      <c r="F14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" t="s">
+        <v>353</v>
+      </c>
+      <c r="I14" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9">
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>372</v>
+      </c>
+      <c r="D15" t="s">
+        <v>237</v>
+      </c>
+      <c r="E15" t="s">
+        <v>373</v>
+      </c>
+      <c r="F15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" t="s">
+        <v>353</v>
+      </c>
+      <c r="I15" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9">
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>374</v>
+      </c>
+      <c r="D16" t="s">
+        <v>237</v>
+      </c>
+      <c r="E16" t="s">
+        <v>375</v>
+      </c>
+      <c r="F16" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" t="s">
+        <v>353</v>
+      </c>
+      <c r="I16" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>376</v>
+      </c>
+      <c r="D17" t="s">
+        <v>237</v>
+      </c>
+      <c r="E17" t="s">
+        <v>377</v>
+      </c>
+      <c r="F17" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" t="s">
+        <v>353</v>
+      </c>
+      <c r="I17" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>378</v>
+      </c>
+      <c r="D18" t="s">
+        <v>237</v>
+      </c>
+      <c r="E18" t="s">
+        <v>379</v>
+      </c>
+      <c r="F18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H18" t="s">
+        <v>353</v>
+      </c>
+      <c r="I18" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>380</v>
+      </c>
+      <c r="D19" t="s">
+        <v>237</v>
+      </c>
+      <c r="E19" t="s">
+        <v>381</v>
+      </c>
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19" t="s">
+        <v>353</v>
+      </c>
+      <c r="I19" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>382</v>
+      </c>
+      <c r="D20" t="s">
+        <v>237</v>
+      </c>
+      <c r="E20" t="s">
+        <v>383</v>
+      </c>
+      <c r="F20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" t="s">
+        <v>353</v>
+      </c>
+      <c r="I20" t="s">
+        <v>241</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -5947,7 +6163,7 @@
     </row>
     <row r="9" spans="2:12">
       <c r="D9" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E9" s="11">
         <v>0</v>
@@ -5958,7 +6174,7 @@
     </row>
     <row r="10" spans="2:12">
       <c r="D10" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E10" s="11">
         <v>0</v>
@@ -5969,7 +6185,7 @@
     </row>
     <row r="11" spans="2:12">
       <c r="D11" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E11" s="11">
         <v>0</v>
@@ -6031,16 +6247,21 @@
         <v>8888</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>68</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" spans="2:14" ht="12.75">
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
+      <c r="D18" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="F18" s="11">
+        <v>8888</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>235</v>
+      </c>
       <c r="H18" s="13"/>
       <c r="I18" s="13"/>
       <c r="J18" s="13"/>
@@ -6428,13 +6649,13 @@
     <row r="2" spans="1:14" ht="17.649999999999999" thickBot="1">
       <c r="A2" s="13"/>
       <c r="B2" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L2" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
@@ -6442,7 +6663,7 @@
     <row r="3" spans="1:14" ht="15" thickTop="1" thickBot="1">
       <c r="A3" s="13"/>
       <c r="B3" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>49</v>
@@ -6451,10 +6672,10 @@
         <v>51</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I3" s="4">
         <v>2022</v>
@@ -6463,23 +6684,23 @@
         <v>56</v>
       </c>
       <c r="L3" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="M3" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="13.15">
       <c r="A4" s="13"/>
       <c r="B4" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C4" s="6"/>
       <c r="F4" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I4" s="11">
         <v>0.05</v>
@@ -6488,10 +6709,10 @@
         <v>25</v>
       </c>
       <c r="L4" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="M4" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="N4" s="6">
         <v>1055.55</v>
@@ -6500,13 +6721,13 @@
     <row r="5" spans="1:14" ht="13.15">
       <c r="A5" s="13"/>
       <c r="B5" s="19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E5" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="F5" s="11" t="s">
         <v>186</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>187</v>
       </c>
       <c r="I5" s="11">
         <v>1</v>
@@ -6515,10 +6736,10 @@
         <v>25</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N5" s="6">
         <v>3.6</v>
@@ -6527,19 +6748,19 @@
     <row r="6" spans="1:14" ht="13.15">
       <c r="A6" s="13"/>
       <c r="B6" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I6" s="11">
         <v>2025</v>
       </c>
       <c r="L6" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="M6" s="6" t="s">
         <v>89</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>90</v>
       </c>
       <c r="N6" s="6">
         <v>1000</v>
@@ -6548,19 +6769,19 @@
     <row r="7" spans="1:14" ht="13.15">
       <c r="A7" s="13"/>
       <c r="B7" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I7" s="11">
         <v>1</v>
       </c>
       <c r="L7" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="M7" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>93</v>
       </c>
       <c r="N7" s="6">
         <v>1000</v>
@@ -6569,25 +6790,25 @@
     <row r="8" spans="1:14" ht="13.15">
       <c r="A8" s="13"/>
       <c r="B8" s="19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I8" s="11">
         <v>2.2201</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N8" s="6">
         <v>1.05555</v>
@@ -6596,25 +6817,25 @@
     <row r="9" spans="1:14" ht="13.15">
       <c r="A9" s="13"/>
       <c r="B9" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I9" s="11">
         <v>2.1427</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N9" s="6">
         <v>4.1868000000000002E-2</v>
@@ -6623,25 +6844,25 @@
     <row r="10" spans="1:14" ht="13.15">
       <c r="A10" s="13"/>
       <c r="B10" s="19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I10" s="11">
         <v>2.077</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N10" s="6">
         <v>41.868000000000002</v>
@@ -6650,25 +6871,25 @@
     <row r="11" spans="1:14" ht="13.15">
       <c r="A11" s="13"/>
       <c r="B11" s="19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I11" s="11">
         <v>2.0358000000000001</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N11" s="6">
         <v>3.5999999999999999E-3</v>
@@ -6677,25 +6898,25 @@
     <row r="12" spans="1:14" ht="13.15">
       <c r="A12" s="13"/>
       <c r="B12" s="19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I12" s="11">
         <v>1.9870000000000001</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N12" s="6">
         <v>1000000</v>
@@ -6704,25 +6925,25 @@
     <row r="13" spans="1:14" ht="13.15">
       <c r="A13" s="13"/>
       <c r="B13" s="19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I13" s="11">
         <v>1.9192</v>
       </c>
       <c r="L13" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="M13" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="N13" s="6">
         <v>1000</v>
@@ -6731,25 +6952,25 @@
     <row r="14" spans="1:14" ht="13.15">
       <c r="A14" s="13"/>
       <c r="B14" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I14" s="11">
         <v>1.8468</v>
       </c>
       <c r="L14" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="M14" s="6" t="s">
         <v>108</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>109</v>
       </c>
       <c r="N14" s="6">
         <v>5.8615199999999996</v>
@@ -6758,25 +6979,25 @@
     <row r="15" spans="1:14" ht="13.15">
       <c r="A15" s="13"/>
       <c r="B15" s="19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I15" s="11">
         <v>1.7799</v>
       </c>
       <c r="L15" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="M15" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="N15" s="6">
         <v>1E-3</v>
@@ -6785,25 +7006,25 @@
     <row r="16" spans="1:14" ht="13.15">
       <c r="A16" s="13"/>
       <c r="B16" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I16" s="11">
         <v>1.722</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N16" s="6">
         <v>1000</v>
@@ -6812,25 +7033,25 @@
     <row r="17" spans="1:14" ht="13.15">
       <c r="A17" s="13"/>
       <c r="B17" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I17" s="11">
         <v>1.6836</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N17" s="6">
         <v>37.68</v>
@@ -6838,25 +7059,25 @@
     </row>
     <row r="18" spans="1:14" ht="13.15">
       <c r="B18" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I18" s="11">
         <v>1.6446000000000001</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N18" s="6">
         <v>2139.4548</v>
@@ -6864,25 +7085,25 @@
     </row>
     <row r="19" spans="1:14" ht="13.15">
       <c r="B19" s="19" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I19" s="11">
         <v>1.6102000000000001</v>
       </c>
       <c r="L19" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="M19" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="M19" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="N19" s="6">
         <v>2.78</v>
@@ -6890,25 +7111,25 @@
     </row>
     <row r="20" spans="1:14" ht="13.15">
       <c r="B20" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I20" s="11">
         <v>1.5770999999999999</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N20" s="6">
         <v>3.6</v>
@@ -6916,25 +7137,25 @@
     </row>
     <row r="21" spans="1:14" ht="13.15">
       <c r="B21" s="19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I21" s="11">
         <v>1.5488</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N21" s="6">
         <v>1</v>
@@ -6942,25 +7163,25 @@
     </row>
     <row r="22" spans="1:14" ht="13.15">
       <c r="B22" s="19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I22" s="11">
         <v>1.5224</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N22" s="6">
         <v>31.536000000000001</v>
@@ -6968,25 +7189,25 @@
     </row>
     <row r="23" spans="1:14" ht="13.15">
       <c r="B23" s="19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I23" s="11">
         <v>1.5058</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N23" s="6">
         <v>120</v>
@@ -6994,25 +7215,25 @@
     </row>
     <row r="24" spans="1:14" ht="13.15">
       <c r="B24" s="19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I24" s="11">
         <v>1.4844999999999999</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N24" s="11">
         <v>5.8615199999999996</v>
@@ -7020,25 +7241,25 @@
     </row>
     <row r="25" spans="1:14" ht="13.15">
       <c r="B25" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I25" s="11">
         <v>1.4518</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M25" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N25" s="11">
         <v>54</v>
@@ -7046,16 +7267,16 @@
     </row>
     <row r="26" spans="1:14" ht="13.15">
       <c r="B26" s="19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I26" s="11">
         <v>1.4198999999999999</v>
@@ -7063,16 +7284,16 @@
     </row>
     <row r="27" spans="1:14" ht="13.15">
       <c r="B27" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I27" s="11">
         <v>1.3986000000000001</v>
@@ -7080,16 +7301,16 @@
     </row>
     <row r="28" spans="1:14" ht="13.15">
       <c r="B28" s="19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I28" s="11">
         <v>1.3727</v>
@@ -7097,16 +7318,16 @@
     </row>
     <row r="29" spans="1:14" ht="13.15">
       <c r="B29" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I29" s="11">
         <v>1.3369</v>
@@ -7114,16 +7335,16 @@
     </row>
     <row r="30" spans="1:14" ht="13.15">
       <c r="B30" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I30" s="11">
         <v>1.2967</v>
@@ -7131,16 +7352,16 @@
     </row>
     <row r="31" spans="1:14" ht="13.15">
       <c r="B31" s="19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I31" s="11">
         <v>1.2583</v>
@@ -7148,16 +7369,16 @@
     </row>
     <row r="32" spans="1:14" ht="13.15">
       <c r="B32" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I32" s="11">
         <v>1.2253000000000001</v>
@@ -7165,16 +7386,16 @@
     </row>
     <row r="33" spans="2:9" ht="13.15">
       <c r="B33" s="19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I33" s="11">
         <v>1.2023999999999999</v>
@@ -7182,16 +7403,16 @@
     </row>
     <row r="34" spans="2:9" ht="13.15">
       <c r="B34" s="19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I34" s="11">
         <v>1.1931</v>
@@ -7199,16 +7420,16 @@
     </row>
     <row r="35" spans="2:9" ht="13.15">
       <c r="B35" s="19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I35" s="11">
         <v>1.1793</v>
@@ -7216,16 +7437,16 @@
     </row>
     <row r="36" spans="2:9" ht="13.15">
       <c r="B36" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I36" s="11">
         <v>1.1552</v>
@@ -7233,16 +7454,16 @@
     </row>
     <row r="37" spans="2:9" ht="13.15">
       <c r="B37" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I37" s="11">
         <v>1.1334</v>
@@ -7250,16 +7471,16 @@
     </row>
     <row r="38" spans="2:9" ht="13.15">
       <c r="B38" s="19" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I38" s="11">
         <v>1.1136999999999999</v>
@@ -7267,16 +7488,16 @@
     </row>
     <row r="39" spans="2:9" ht="13.15">
       <c r="B39" s="19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I39" s="11">
         <v>1.0934999999999999</v>
@@ -7284,16 +7505,16 @@
     </row>
     <row r="40" spans="2:9" ht="13.15">
       <c r="B40" s="19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I40" s="11">
         <v>1.0831</v>
@@ -7301,16 +7522,16 @@
     </row>
     <row r="41" spans="2:9" ht="13.15">
       <c r="B41" s="19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I41" s="11">
         <v>1.0719000000000001</v>
@@ -7318,16 +7539,16 @@
     </row>
     <row r="42" spans="2:9" ht="13.15">
       <c r="B42" s="19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I42" s="11">
         <v>1.0519000000000001</v>
@@ -7335,16 +7556,16 @@
     </row>
     <row r="43" spans="2:9" ht="13.15">
       <c r="B43" s="19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I43" s="11">
         <v>1.0274000000000001</v>
@@ -7352,16 +7573,16 @@
     </row>
     <row r="44" spans="2:9" ht="13.15">
       <c r="B44" s="19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I44" s="11">
         <v>1.0091000000000001</v>
@@ -7369,16 +7590,16 @@
     </row>
     <row r="45" spans="2:9" ht="13.15">
       <c r="B45" s="19" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I45" s="11">
         <v>1</v>
@@ -7386,16 +7607,16 @@
     </row>
     <row r="46" spans="2:9" ht="13.15">
       <c r="B46" s="19" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I46" s="11">
         <v>0.98960000000000004</v>
@@ -7403,16 +7624,16 @@
     </row>
     <row r="47" spans="2:9" ht="13.15">
       <c r="B47" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I47" s="11">
         <v>0.97809999999999997</v>
@@ -7420,16 +7641,16 @@
     </row>
     <row r="48" spans="2:9" ht="13.15">
       <c r="B48" s="19" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I48" s="11">
         <v>0.96499999999999997</v>
@@ -7437,16 +7658,16 @@
     </row>
     <row r="49" spans="2:9" ht="13.15">
       <c r="B49" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I49" s="11">
         <v>0.94910000000000005</v>
@@ -7454,16 +7675,16 @@
     </row>
     <row r="50" spans="2:9" ht="13.15">
       <c r="B50" s="19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I50" s="11">
         <v>0.92969999999999997</v>
@@ -7471,7 +7692,7 @@
     </row>
     <row r="51" spans="2:9" ht="13.15">
       <c r="B51" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F51" s="11" t="str">
         <f>F46</f>
@@ -7482,7 +7703,7 @@
         <v>USD20</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I51" s="11">
         <f t="shared" si="0"/>
@@ -7491,13 +7712,13 @@
     </row>
     <row r="52" spans="2:9" ht="13.15">
       <c r="B52" s="19" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I52" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7505,13 +7726,13 @@
     </row>
     <row r="53" spans="2:9" ht="13.15">
       <c r="B53" s="19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I53" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7519,13 +7740,13 @@
     </row>
     <row r="54" spans="2:9" ht="13.15">
       <c r="B54" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I54" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7533,10 +7754,10 @@
     </row>
     <row r="55" spans="2:9">
       <c r="F55" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I55" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7544,10 +7765,10 @@
     </row>
     <row r="56" spans="2:9">
       <c r="F56" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I56" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7555,10 +7776,10 @@
     </row>
     <row r="57" spans="2:9">
       <c r="F57" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I57" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7566,10 +7787,10 @@
     </row>
     <row r="58" spans="2:9">
       <c r="F58" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I58" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7577,10 +7798,10 @@
     </row>
     <row r="59" spans="2:9">
       <c r="F59" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I59" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7588,10 +7809,10 @@
     </row>
     <row r="60" spans="2:9">
       <c r="F60" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I60" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7599,10 +7820,10 @@
     </row>
     <row r="61" spans="2:9">
       <c r="F61" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I61" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7610,10 +7831,10 @@
     </row>
     <row r="62" spans="2:9">
       <c r="F62" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I62" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7621,10 +7842,10 @@
     </row>
     <row r="63" spans="2:9">
       <c r="F63" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I63" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7632,10 +7853,10 @@
     </row>
     <row r="64" spans="2:9">
       <c r="F64" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I64" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7643,10 +7864,10 @@
     </row>
     <row r="65" spans="6:9">
       <c r="F65" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I65" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7654,10 +7875,10 @@
     </row>
     <row r="66" spans="6:9">
       <c r="F66" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I66" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7665,10 +7886,10 @@
     </row>
     <row r="67" spans="6:9">
       <c r="F67" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I67" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7676,10 +7897,10 @@
     </row>
     <row r="68" spans="6:9">
       <c r="F68" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I68" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7687,10 +7908,10 @@
     </row>
     <row r="69" spans="6:9">
       <c r="F69" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I69" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7698,10 +7919,10 @@
     </row>
     <row r="70" spans="6:9">
       <c r="F70" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I70" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7709,10 +7930,10 @@
     </row>
     <row r="71" spans="6:9">
       <c r="F71" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I71" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7720,10 +7941,10 @@
     </row>
     <row r="72" spans="6:9">
       <c r="F72" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I72" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7731,10 +7952,10 @@
     </row>
     <row r="73" spans="6:9">
       <c r="F73" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I73" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7742,10 +7963,10 @@
     </row>
     <row r="74" spans="6:9">
       <c r="F74" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I74" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7753,10 +7974,10 @@
     </row>
     <row r="75" spans="6:9">
       <c r="F75" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I75" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7764,10 +7985,10 @@
     </row>
     <row r="76" spans="6:9">
       <c r="F76" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I76" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7775,10 +7996,10 @@
     </row>
     <row r="77" spans="6:9">
       <c r="F77" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H77" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I77" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7786,10 +8007,10 @@
     </row>
     <row r="78" spans="6:9">
       <c r="F78" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I78" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7797,10 +8018,10 @@
     </row>
     <row r="79" spans="6:9">
       <c r="F79" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I79" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7808,10 +8029,10 @@
     </row>
     <row r="80" spans="6:9">
       <c r="F80" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I80" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7819,10 +8040,10 @@
     </row>
     <row r="81" spans="6:9">
       <c r="F81" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H81" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I81" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7830,10 +8051,10 @@
     </row>
     <row r="82" spans="6:9">
       <c r="F82" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I82" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7841,10 +8062,10 @@
     </row>
     <row r="83" spans="6:9">
       <c r="F83" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H83" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I83" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7852,10 +8073,10 @@
     </row>
     <row r="84" spans="6:9">
       <c r="F84" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H84" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I84" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7863,10 +8084,10 @@
     </row>
     <row r="85" spans="6:9">
       <c r="F85" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H85" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I85" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7874,10 +8095,10 @@
     </row>
     <row r="86" spans="6:9">
       <c r="F86" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H86" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I86" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7885,10 +8106,10 @@
     </row>
     <row r="87" spans="6:9">
       <c r="F87" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H87" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I87" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7896,10 +8117,10 @@
     </row>
     <row r="88" spans="6:9">
       <c r="F88" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H88" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I88" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7907,10 +8128,10 @@
     </row>
     <row r="89" spans="6:9">
       <c r="F89" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H89" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I89" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7918,10 +8139,10 @@
     </row>
     <row r="90" spans="6:9">
       <c r="F90" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I90" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7929,10 +8150,10 @@
     </row>
     <row r="91" spans="6:9">
       <c r="F91" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H91" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I91" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7940,10 +8161,10 @@
     </row>
     <row r="92" spans="6:9">
       <c r="F92" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I92" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7951,10 +8172,10 @@
     </row>
     <row r="93" spans="6:9">
       <c r="F93" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H93" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I93" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7962,10 +8183,10 @@
     </row>
     <row r="94" spans="6:9">
       <c r="F94" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I94" s="11">
         <v>7.0000000000000007E-2</v>
@@ -7973,7 +8194,7 @@
     </row>
     <row r="95" spans="6:9">
       <c r="F95" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H95" s="11" t="str">
         <f>H51</f>
@@ -7985,7 +8206,7 @@
     </row>
     <row r="99" spans="5:10" ht="17.649999999999999" thickBot="1">
       <c r="E99" s="20" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="100" spans="5:10" ht="15" thickTop="1" thickBot="1">
@@ -7996,10 +8217,10 @@
         <v>51</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I100" s="4">
         <v>2022</v>
@@ -8011,13 +8232,13 @@
     <row r="101" spans="5:10" ht="14.25">
       <c r="E101"/>
       <c r="F101" s="21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G101" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H101" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I101" s="22">
         <f>1.10926234054354*I40</f>
@@ -8027,11 +8248,11 @@
     <row r="102" spans="5:10" ht="14.25">
       <c r="E102"/>
       <c r="F102" s="21" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G102"/>
       <c r="H102" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I102" s="22">
         <f>I84</f>
@@ -8064,7 +8285,7 @@
         <v>51</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>53</v>
@@ -8072,10 +8293,10 @@
     </row>
     <row r="5" spans="2:4">
       <c r="B5" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="D5" s="6">
         <v>-1</v>
@@ -8083,10 +8304,10 @@
     </row>
     <row r="6" spans="2:4">
       <c r="B6" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D6" s="6">
         <v>1</v>
@@ -8094,10 +8315,10 @@
     </row>
     <row r="7" spans="2:4">
       <c r="B7" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D7" s="6">
         <v>1</v>
@@ -8105,10 +8326,10 @@
     </row>
     <row r="8" spans="2:4">
       <c r="B8" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D8" s="6">
         <v>1</v>
@@ -8116,10 +8337,10 @@
     </row>
     <row r="9" spans="2:4">
       <c r="B9" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D9" s="6">
         <v>1</v>
@@ -8127,10 +8348,10 @@
     </row>
     <row r="10" spans="2:4">
       <c r="B10" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D10" s="6">
         <v>1</v>
@@ -8138,10 +8359,10 @@
     </row>
     <row r="11" spans="2:4">
       <c r="B11" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D11" s="6">
         <v>1</v>
@@ -8149,10 +8370,10 @@
     </row>
     <row r="12" spans="2:4">
       <c r="B12" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D12" s="6">
         <v>1</v>
@@ -8160,10 +8381,10 @@
     </row>
     <row r="13" spans="2:4">
       <c r="B13" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D13" s="6">
         <v>1</v>
@@ -8171,10 +8392,10 @@
     </row>
     <row r="14" spans="2:4">
       <c r="B14" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D14" s="6">
         <v>2</v>
@@ -8182,10 +8403,10 @@
     </row>
     <row r="15" spans="2:4">
       <c r="B15" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D15" s="6">
         <v>1</v>
@@ -8193,10 +8414,10 @@
     </row>
     <row r="16" spans="2:4">
       <c r="B16" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D16" s="16">
         <v>1.0000000000000001E-5</v>
@@ -8204,10 +8425,10 @@
     </row>
     <row r="17" spans="2:4">
       <c r="B17" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D17" s="16">
         <v>1.0000000000000001E-5</v>
@@ -8215,10 +8436,10 @@
     </row>
     <row r="18" spans="2:4">
       <c r="B18" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D18" s="16">
         <v>1.0000000000000001E-5</v>
@@ -8226,10 +8447,10 @@
     </row>
     <row r="19" spans="2:4">
       <c r="B19" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D19" s="16">
         <v>1.0000000000000001E-5</v>
@@ -8237,10 +8458,10 @@
     </row>
     <row r="20" spans="2:4">
       <c r="B20" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>169</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>170</v>
       </c>
       <c r="D20" s="17">
         <v>1</v>
@@ -8248,73 +8469,73 @@
     </row>
     <row r="23" spans="2:4">
       <c r="B23" s="18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="17.649999999999999" thickBot="1">
       <c r="B25" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="26" spans="2:4" ht="15" thickTop="1" thickBot="1">
       <c r="B26" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="27" spans="2:4">
       <c r="B27" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="28" spans="2:4">
       <c r="B28" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="2:4">
       <c r="B29" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="2:4">
       <c r="B30" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="2:4">
       <c r="B31" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="2:4">
       <c r="B32" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="B33" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
